--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0006.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0006.xlsx
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
@@ -35504,7 +35504,7 @@
       </c>
       <c r="M501" t="inlineStr">
         <is>
-          <t>Progress</t>
+          <t>Tiến độ</t>
         </is>
       </c>
       <c r="N501" t="inlineStr">
